--- a/jpcore-r4b/develop/StructureDefinition-JP-ServiceRequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-ServiceRequest.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-JP-ServiceRequest.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-ServiceRequest.xlsx
@@ -432,7 +432,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -452,7 +452,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -791,7 +791,7 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](task.html) resource.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](http://hl7.org/fhir/R4B/event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4B/task.html) resource.</t>
   </si>
   <si>
     <t>required</t>
@@ -1306,7 +1306,7 @@
     <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4B/servicerequest-example-di.html).</t>
   </si>
   <si>
     <t>SNOMED CT Condition/Problem/Diagnosis Codes</t>
@@ -1340,7 +1340,7 @@
     <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4B/servicerequest-example-di.html).</t>
   </si>
   <si>
     <t>Request.reasonReference</t>
@@ -1416,7 +1416,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](specimen.html) resource points to the ServiceRequest.</t>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4B/specimen.html) resource points to the ServiceRequest.</t>
   </si>
   <si>
     <t>SPM</t>
